--- a/team-logo-image-downloads.xlsx
+++ b/team-logo-image-downloads.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulb/Library/CloudStorage/Dropbox/home/tech/website/sportspuff/logos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulb/Documents/version-control/git/sportspuff-v6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DD68EB-7939-3E47-B86E-F04D41DAFAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B57AA68-27C1-7449-AB23-7EBF20412BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="680" windowWidth="29400" windowHeight="20620" activeTab="1" xr2:uid="{A3B21BBA-03DF-F54B-8D92-2B97C02F6BEF}"/>
+    <workbookView xWindow="980" yWindow="660" windowWidth="29960" windowHeight="12380" xr2:uid="{A3B21BBA-03DF-F54B-8D92-2B97C02F6BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="leagues-and-teams" sheetId="1" r:id="rId1"/>
@@ -1099,7 +1099,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3722" uniqueCount="1583">
   <si>
     <t>las_vegas</t>
   </si>
@@ -4278,9 +4278,6 @@
     <t>Grass</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>44°57′10″N 93°9′54″W</t>
   </si>
   <si>
@@ -5788,6 +5785,69 @@
   </si>
   <si>
     <t>logo_filename</t>
+  </si>
+  <si>
+    <t>Los Angeles Knight Riders</t>
+  </si>
+  <si>
+    <t>MI New York</t>
+  </si>
+  <si>
+    <t>San Francisco Unicorns</t>
+  </si>
+  <si>
+    <t>Seattle Orcas</t>
+  </si>
+  <si>
+    <t>Texas Super Kings</t>
+  </si>
+  <si>
+    <t>Washington Freedom</t>
+  </si>
+  <si>
+    <t>MLC</t>
+  </si>
+  <si>
+    <t>mlc</t>
+  </si>
+  <si>
+    <t>Major League Cricket</t>
+  </si>
+  <si>
+    <t>washington_</t>
+  </si>
+  <si>
+    <t>Knight Riders Cricket Field at Fairplex</t>
+  </si>
+  <si>
+    <t>Pomona, CA</t>
+  </si>
+  <si>
+    <t>pomona</t>
+  </si>
+  <si>
+    <t>california</t>
+  </si>
+  <si>
+    <t>Grand Prairie Stadium</t>
+  </si>
+  <si>
+    <t>Grand Prairie, TX</t>
+  </si>
+  <si>
+    <t>grand_prairie</t>
+  </si>
+  <si>
+    <t>texas</t>
+  </si>
+  <si>
+    <t>Oakland Coliseum</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>oakland</t>
   </si>
 </sst>
 </file>
@@ -5848,7 +5908,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -5871,12 +5931,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5901,6 +5972,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6855,7 +6929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63105598-E035-4B4A-AEFD-23E362AE6639}">
-  <dimension ref="A1:U185"/>
+  <dimension ref="A1:U192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
@@ -6937,7 +7011,7 @@
         <v>374</v>
       </c>
       <c r="S1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="T1" t="s">
         <v>1024</v>
@@ -18353,19 +18427,19 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B175" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C175" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D175">
         <v>7</v>
       </c>
       <c r="E175" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="F175">
         <v>1173</v>
@@ -18389,16 +18463,16 @@
         <v>913</v>
       </c>
       <c r="M175" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N175" s="3">
         <v>100</v>
       </c>
       <c r="O175" t="s">
+        <v>1501</v>
+      </c>
+      <c r="P175" t="s">
         <v>1502</v>
-      </c>
-      <c r="P175" t="s">
-        <v>1503</v>
       </c>
       <c r="Q175" t="s">
         <v>976</v>
@@ -18408,27 +18482,27 @@
         <v>ipl_logo.png</v>
       </c>
       <c r="T175" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="U175" s="4"/>
     </row>
     <row r="176" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" t="str">
-        <f t="shared" ref="A176:A185" si="3">SUBSTITUTE(C176," ","_")</f>
+        <f t="shared" ref="A176:A186" si="3">SUBSTITUTE(C176," ","_")</f>
         <v>Chennai_Super_Kings </v>
       </c>
       <c r="B176" t="str">
-        <f t="shared" ref="B176:B185" si="4">SUBSTITUTE(LOWER(C176)," ","_")</f>
+        <f t="shared" ref="B176:B186" si="4">SUBSTITUTE(LOWER(C176)," ","_")</f>
         <v>chennai_super_kings </v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D176">
         <v>7</v>
       </c>
       <c r="E176" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F176">
         <v>1174</v>
@@ -18437,28 +18511,29 @@
         <v>136</v>
       </c>
       <c r="H176" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I176" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J176">
         <v>118</v>
       </c>
       <c r="K176" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L176" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N176" s="2">
+        <f>N175+1</f>
         <v>101</v>
       </c>
       <c r="O176" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="P176" t="s">
         <v>975</v>
@@ -18488,48 +18563,48 @@
         <v>delhi_capitals</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D177">
         <v>7</v>
       </c>
       <c r="E177" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F177">
-        <f t="shared" ref="F177:F185" si="5">F176+1</f>
+        <f t="shared" ref="F177:F192" si="5">F176+1</f>
         <v>1175</v>
       </c>
       <c r="G177">
         <v>136</v>
       </c>
       <c r="H177" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I177" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J177">
         <v>118</v>
       </c>
       <c r="K177" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L177" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N177" s="2">
         <f>N176+1</f>
         <v>102</v>
       </c>
       <c r="O177" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="P177" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="Q177" t="s">
         <v>976</v>
@@ -18556,13 +18631,13 @@
         <v>gujarat_titans</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D178">
         <v>7</v>
       </c>
       <c r="E178" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F178">
         <f t="shared" si="5"/>
@@ -18572,32 +18647,32 @@
         <v>136</v>
       </c>
       <c r="H178" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I178" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J178">
         <v>118</v>
       </c>
       <c r="K178" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L178" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N178" s="2">
         <f t="shared" ref="N178:N185" si="7">N177+1</f>
         <v>103</v>
       </c>
       <c r="O178" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="P178" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="Q178" t="s">
         <v>976</v>
@@ -18624,13 +18699,13 @@
         <v>kolkata_knight_riders</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D179">
         <v>7</v>
       </c>
       <c r="E179" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F179">
         <f t="shared" si="5"/>
@@ -18640,32 +18715,32 @@
         <v>136</v>
       </c>
       <c r="H179" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I179" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J179">
         <v>118</v>
       </c>
       <c r="K179" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L179" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N179" s="2">
         <f t="shared" si="7"/>
         <v>104</v>
       </c>
       <c r="O179" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="P179" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="Q179" t="s">
         <v>976</v>
@@ -18692,13 +18767,13 @@
         <v>lucknow_super_giants</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D180">
         <v>7</v>
       </c>
       <c r="E180" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F180">
         <f t="shared" si="5"/>
@@ -18708,32 +18783,32 @@
         <v>136</v>
       </c>
       <c r="H180" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I180" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J180">
         <v>118</v>
       </c>
       <c r="K180" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L180" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N180" s="2">
         <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="O180" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="P180" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="Q180" t="s">
         <v>976</v>
@@ -18760,13 +18835,13 @@
         <v>mumbai_indians</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D181">
         <v>7</v>
       </c>
       <c r="E181" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F181">
         <f t="shared" si="5"/>
@@ -18776,32 +18851,32 @@
         <v>136</v>
       </c>
       <c r="H181" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I181" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J181">
         <v>118</v>
       </c>
       <c r="K181" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L181" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N181" s="2">
         <f t="shared" si="7"/>
         <v>106</v>
       </c>
       <c r="O181" t="s">
+        <v>1501</v>
+      </c>
+      <c r="P181" t="s">
         <v>1502</v>
-      </c>
-      <c r="P181" t="s">
-        <v>1503</v>
       </c>
       <c r="Q181" t="s">
         <v>976</v>
@@ -18828,13 +18903,13 @@
         <v>punjab_kings</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D182">
         <v>7</v>
       </c>
       <c r="E182" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F182">
         <f t="shared" si="5"/>
@@ -18844,32 +18919,32 @@
         <v>136</v>
       </c>
       <c r="H182" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I182" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J182">
         <v>118</v>
       </c>
       <c r="K182" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L182" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N182" s="2">
         <f t="shared" si="7"/>
         <v>107</v>
       </c>
       <c r="O182" t="s">
+        <v>1527</v>
+      </c>
+      <c r="P182" t="s">
         <v>1528</v>
-      </c>
-      <c r="P182" t="s">
-        <v>1529</v>
       </c>
       <c r="Q182" t="s">
         <v>976</v>
@@ -18896,13 +18971,13 @@
         <v>rajasthan_royals</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D183">
         <v>7</v>
       </c>
       <c r="E183" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F183">
         <f t="shared" si="5"/>
@@ -18912,32 +18987,32 @@
         <v>136</v>
       </c>
       <c r="H183" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I183" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J183">
         <v>118</v>
       </c>
       <c r="K183" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L183" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N183" s="2">
         <f t="shared" si="7"/>
         <v>108</v>
       </c>
       <c r="O183" t="s">
+        <v>1529</v>
+      </c>
+      <c r="P183" t="s">
         <v>1530</v>
-      </c>
-      <c r="P183" t="s">
-        <v>1531</v>
       </c>
       <c r="Q183" t="s">
         <v>976</v>
@@ -18964,13 +19039,13 @@
         <v>royal_challengers_bengaluru</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D184">
         <v>7</v>
       </c>
       <c r="E184" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F184">
         <f t="shared" si="5"/>
@@ -18980,32 +19055,32 @@
         <v>136</v>
       </c>
       <c r="H184" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I184" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J184">
         <v>118</v>
       </c>
       <c r="K184" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L184" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N184" s="2">
         <f t="shared" si="7"/>
         <v>109</v>
       </c>
       <c r="O184" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="P184" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="Q184" t="s">
         <v>976</v>
@@ -19032,13 +19107,13 @@
         <v>sunrisers_hyderabad</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D185">
         <v>7</v>
       </c>
       <c r="E185" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F185">
         <f t="shared" si="5"/>
@@ -19048,32 +19123,32 @@
         <v>136</v>
       </c>
       <c r="H185" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="I185" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J185">
         <v>118</v>
       </c>
       <c r="K185" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="L185" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N185" s="2">
         <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="O185" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="P185" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="Q185" t="s">
         <v>976</v>
@@ -19088,6 +19163,448 @@
       <c r="T185" t="str">
         <f t="shared" si="6"/>
         <v>sunrisers_hyderabad_logo.png</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D186">
+        <v>8</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F186">
+        <f t="shared" si="5"/>
+        <v>1184</v>
+      </c>
+      <c r="G186">
+        <v>137</v>
+      </c>
+      <c r="H186" t="s">
+        <v>375</v>
+      </c>
+      <c r="I186" t="s">
+        <v>913</v>
+      </c>
+      <c r="J186">
+        <v>119</v>
+      </c>
+      <c r="K186" t="s">
+        <v>375</v>
+      </c>
+      <c r="L186" t="s">
+        <v>913</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N186" s="2">
+        <v>100</v>
+      </c>
+      <c r="O186" t="s">
+        <v>376</v>
+      </c>
+      <c r="P186" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>378</v>
+      </c>
+      <c r="S186" t="str">
+        <f t="shared" ref="S186:S192" si="8">B186&amp;"_logo.png"</f>
+        <v>mlc_logo.png</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A187" t="str">
+        <f t="shared" ref="A187:A191" si="9">SUBSTITUTE(C187," ","_")</f>
+        <v>Los_Angeles_Knight_Riders</v>
+      </c>
+      <c r="B187" t="str">
+        <f t="shared" ref="B187:B191" si="10">SUBSTITUTE(LOWER(C187)," ","_")</f>
+        <v>los_angeles_knight_riders</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D187">
+        <v>8</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F187">
+        <f t="shared" si="5"/>
+        <v>1185</v>
+      </c>
+      <c r="G187">
+        <v>138</v>
+      </c>
+      <c r="H187" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I187" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J187">
+        <v>120</v>
+      </c>
+      <c r="K187" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L187" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N187" s="2">
+        <f>N186+1</f>
+        <v>101</v>
+      </c>
+      <c r="O187" t="s">
+        <v>983</v>
+      </c>
+      <c r="P187" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>378</v>
+      </c>
+      <c r="R187">
+        <v>254</v>
+      </c>
+      <c r="S187" t="str">
+        <f t="shared" si="8"/>
+        <v>los_angeles_knight_riders_logo.png</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A188" t="str">
+        <f t="shared" si="9"/>
+        <v>MI_New_York</v>
+      </c>
+      <c r="B188" t="str">
+        <f t="shared" si="10"/>
+        <v>mi_new_york</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D188">
+        <v>8</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F188">
+        <f t="shared" si="5"/>
+        <v>1186</v>
+      </c>
+      <c r="G188">
+        <v>138</v>
+      </c>
+      <c r="H188" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J188">
+        <v>120</v>
+      </c>
+      <c r="K188" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L188" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N188" s="2">
+        <f t="shared" ref="N188:N192" si="11">N187+1</f>
+        <v>102</v>
+      </c>
+      <c r="O188" t="s">
+        <v>376</v>
+      </c>
+      <c r="P188" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>378</v>
+      </c>
+      <c r="R188">
+        <v>253</v>
+      </c>
+      <c r="S188" t="str">
+        <f t="shared" si="8"/>
+        <v>mi_new_york_logo.png</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A189" t="str">
+        <f t="shared" si="9"/>
+        <v>San_Francisco_Unicorns</v>
+      </c>
+      <c r="B189" t="str">
+        <f t="shared" si="10"/>
+        <v>san_francisco_unicorns</v>
+      </c>
+      <c r="C189" s="16" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D189">
+        <v>8</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F189">
+        <f t="shared" si="5"/>
+        <v>1187</v>
+      </c>
+      <c r="G189">
+        <v>138</v>
+      </c>
+      <c r="H189" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I189" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J189">
+        <v>120</v>
+      </c>
+      <c r="K189" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L189" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N189" s="2">
+        <f t="shared" si="11"/>
+        <v>103</v>
+      </c>
+      <c r="O189" t="s">
+        <v>1008</v>
+      </c>
+      <c r="P189" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>378</v>
+      </c>
+      <c r="R189">
+        <v>252</v>
+      </c>
+      <c r="S189" t="str">
+        <f t="shared" si="8"/>
+        <v>san_francisco_unicorns_logo.png</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A190" t="str">
+        <f t="shared" si="9"/>
+        <v>Seattle_Orcas</v>
+      </c>
+      <c r="B190" t="str">
+        <f t="shared" si="10"/>
+        <v>seattle_orcas</v>
+      </c>
+      <c r="C190" s="16" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D190">
+        <v>8</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F190">
+        <f t="shared" si="5"/>
+        <v>1188</v>
+      </c>
+      <c r="G190">
+        <v>138</v>
+      </c>
+      <c r="H190" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J190">
+        <v>120</v>
+      </c>
+      <c r="K190" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L190" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M190" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N190" s="2">
+        <f t="shared" si="11"/>
+        <v>104</v>
+      </c>
+      <c r="O190" t="s">
+        <v>945</v>
+      </c>
+      <c r="P190" t="s">
+        <v>989</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>378</v>
+      </c>
+      <c r="R190">
+        <v>252</v>
+      </c>
+      <c r="S190" t="str">
+        <f t="shared" si="8"/>
+        <v>seattle_orcas_logo.png</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A191" t="str">
+        <f t="shared" si="9"/>
+        <v>Texas_Super_Kings</v>
+      </c>
+      <c r="B191" t="str">
+        <f t="shared" si="10"/>
+        <v>texas_super_kings</v>
+      </c>
+      <c r="C191" s="16" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D191">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F191">
+        <f t="shared" si="5"/>
+        <v>1189</v>
+      </c>
+      <c r="G191">
+        <v>138</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I191" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J191">
+        <v>120</v>
+      </c>
+      <c r="K191" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L191" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N191" s="2">
+        <f t="shared" si="11"/>
+        <v>105</v>
+      </c>
+      <c r="O191" t="s">
+        <v>951</v>
+      </c>
+      <c r="P191" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>378</v>
+      </c>
+      <c r="R191">
+        <v>253</v>
+      </c>
+      <c r="S191" t="str">
+        <f t="shared" si="8"/>
+        <v>texas_super_kings_logo.png</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A192" t="str">
+        <f t="shared" ref="A192" si="12">SUBSTITUTE(C192," ","_")</f>
+        <v>Washington_Freedom</v>
+      </c>
+      <c r="B192" t="str">
+        <f t="shared" ref="B192" si="13">SUBSTITUTE(LOWER(C192)," ","_")</f>
+        <v>washington_freedom</v>
+      </c>
+      <c r="C192" s="16" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D192">
+        <v>8</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F192">
+        <f t="shared" si="5"/>
+        <v>1190</v>
+      </c>
+      <c r="G192">
+        <v>138</v>
+      </c>
+      <c r="H192" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I192" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J192">
+        <v>120</v>
+      </c>
+      <c r="K192" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L192" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N192" s="2">
+        <f t="shared" si="11"/>
+        <v>106</v>
+      </c>
+      <c r="O192" t="s">
+        <v>1571</v>
+      </c>
+      <c r="P192" t="s">
+        <v>1004</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>378</v>
+      </c>
+      <c r="R192">
+        <v>253</v>
+      </c>
+      <c r="S192" t="str">
+        <f t="shared" si="8"/>
+        <v>washington_freedom_logo.png</v>
       </c>
     </row>
   </sheetData>
@@ -19100,12 +19617,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F304D93-8790-9E4B-A36F-D4C0879913D0}">
-  <dimension ref="A1:V152"/>
+  <dimension ref="A1:V158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
@@ -19336,10 +19853,10 @@
         <v>2019</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>1059</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>1060</v>
       </c>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
@@ -19365,16 +19882,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>1061</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>1062</v>
       </c>
       <c r="D5" s="6">
         <v>104</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F5" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19403,7 +19920,7 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
@@ -19413,16 +19930,16 @@
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>1065</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1066</v>
       </c>
       <c r="D6" s="6">
         <v>105</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19448,10 +19965,10 @@
         <v>2008</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
@@ -19477,16 +19994,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>1069</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>1070</v>
       </c>
       <c r="D7" s="6">
         <v>106</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19515,7 +20032,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="S7" s="8"/>
       <c r="T7" s="5"/>
@@ -19527,16 +20044,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>1073</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>1074</v>
       </c>
       <c r="D8" s="6">
         <v>107</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19562,11 +20079,11 @@
         <v>2001</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P8" s="5">
         <v>400</v>
@@ -19585,16 +20102,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>1078</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>1079</v>
       </c>
       <c r="D9" s="6">
         <v>108</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19620,11 +20137,11 @@
         <v>1966</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="P9" s="5">
         <v>396</v>
@@ -19643,16 +20160,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>1082</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1083</v>
       </c>
       <c r="D10" s="6">
         <v>109</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19695,16 +20212,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>1085</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>1086</v>
       </c>
       <c r="D11" s="6">
         <v>110</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19724,13 +20241,13 @@
         <v>80000</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="L11" s="5">
         <v>2009</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="5"/>
@@ -19745,23 +20262,23 @@
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>1089</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>1090</v>
       </c>
       <c r="D12" s="6">
         <v>111</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>washington</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>1004</v>
@@ -19779,10 +20296,10 @@
         <v>2018</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -19808,16 +20325,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>1094</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1095</v>
       </c>
       <c r="D13" s="6">
         <v>112</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19846,7 +20363,7 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S13" s="8"/>
       <c r="T13" s="5"/>
@@ -19856,16 +20373,16 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>1098</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>1099</v>
       </c>
       <c r="D14" s="6">
         <v>113</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19885,16 +20402,16 @@
         <v>38000</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="L14" s="9">
         <v>1996</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -19912,16 +20429,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>1103</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>1104</v>
       </c>
       <c r="D15" s="6">
         <v>114</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19950,7 +20467,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="5"/>
@@ -19960,16 +20477,16 @@
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>1107</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>1108</v>
       </c>
       <c r="D16" s="6">
         <v>115</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -19989,16 +20506,16 @@
         <v>22120</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="L16" s="9">
         <v>1983</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -20024,16 +20541,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>1112</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>1113</v>
       </c>
       <c r="D17" s="6">
         <v>116</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20062,7 +20579,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
@@ -20074,16 +20591,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>1116</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>1117</v>
       </c>
       <c r="D18" s="6">
         <v>117</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F18" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20112,7 +20629,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
@@ -20122,16 +20639,16 @@
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>1120</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>1121</v>
       </c>
       <c r="D19" s="6">
         <v>118</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20151,16 +20668,16 @@
         <v>30991</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L19" s="9">
         <v>2007</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
@@ -20184,16 +20701,16 @@
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>1125</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>1126</v>
       </c>
       <c r="D20" s="6">
         <v>119</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="F20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20219,10 +20736,10 @@
         <v>2018</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -20248,16 +20765,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>1129</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>1130</v>
       </c>
       <c r="D21" s="6">
         <v>120</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20286,7 +20803,7 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
@@ -20298,16 +20815,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>1132</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>1133</v>
       </c>
       <c r="D22" s="6">
         <v>121</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20333,11 +20850,11 @@
         <v>2006</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P22" s="5">
         <v>400</v>
@@ -20356,16 +20873,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>1136</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>1137</v>
       </c>
       <c r="D23" s="6">
         <v>122</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20385,13 +20902,13 @@
         <v>73208</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L23" s="5">
         <v>1975</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -20408,16 +20925,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>1141</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>1142</v>
       </c>
       <c r="D24" s="6">
         <v>123</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20446,7 +20963,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
@@ -20458,16 +20975,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>1145</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>1146</v>
       </c>
       <c r="D25" s="6">
         <v>124</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20496,7 +21013,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
@@ -20508,23 +21025,23 @@
         <v>#VALUE!</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>1148</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>1149</v>
       </c>
       <c r="D26" s="6">
         <v>125</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>washington</v>
       </c>
       <c r="G26" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>1004</v>
@@ -20545,7 +21062,7 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="S26" s="8"/>
       <c r="T26" s="5"/>
@@ -20555,23 +21072,23 @@
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>1151</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>1152</v>
       </c>
       <c r="D27" s="6">
         <v>126</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>washington</v>
       </c>
       <c r="G27" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>1004</v>
@@ -20602,16 +21119,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>1153</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>1154</v>
       </c>
       <c r="D28" s="6">
         <v>127</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20640,7 +21157,7 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="S28" s="8"/>
       <c r="T28" s="5"/>
@@ -20652,16 +21169,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>1157</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>1158</v>
       </c>
       <c r="D29" s="6">
         <v>128</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20681,17 +21198,17 @@
         <v>48330</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L29" s="5">
         <v>1998</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P29" s="5">
         <v>407</v>
@@ -20708,16 +21225,16 @@
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>1161</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>1162</v>
       </c>
       <c r="D30" s="6">
         <v>129</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="F30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20743,10 +21260,10 @@
         <v>2020</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
@@ -20770,16 +21287,16 @@
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>1165</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>1166</v>
       </c>
       <c r="D31" s="6">
         <v>130</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20805,10 +21322,10 @@
         <v>2011</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
@@ -20834,16 +21351,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>1169</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>1170</v>
       </c>
       <c r="D32" s="6">
         <v>131</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="F32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20869,11 +21386,11 @@
         <v>2009</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P32" s="5">
         <v>408</v>
@@ -20892,16 +21409,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>1172</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>1173</v>
       </c>
       <c r="D33" s="6">
         <v>132</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20927,11 +21444,11 @@
         <v>2004</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P33" s="5">
         <v>401</v>
@@ -20950,16 +21467,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>1175</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>1176</v>
       </c>
       <c r="D34" s="6">
         <v>133</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="F34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -20988,7 +21505,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
@@ -20998,16 +21515,16 @@
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>1179</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>1180</v>
       </c>
       <c r="D35" s="6">
         <v>134</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F35" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21046,16 +21563,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>1181</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>1182</v>
       </c>
       <c r="D36" s="6">
         <v>135</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F36" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21081,11 +21598,11 @@
         <v>2000</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P36" s="5">
         <v>412</v>
@@ -21104,16 +21621,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>1184</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>1185</v>
       </c>
       <c r="D37" s="6">
         <v>136</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F37" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21139,11 +21656,11 @@
         <v>1995</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P37" s="5">
         <v>415</v>
@@ -21162,16 +21679,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>1186</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>1187</v>
       </c>
       <c r="D38" s="6">
         <v>137</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="F38" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21200,7 +21717,7 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
       <c r="R38" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S38" s="8"/>
       <c r="T38" s="5"/>
@@ -21212,16 +21729,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>1188</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>1189</v>
       </c>
       <c r="D39" s="6">
         <v>138</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F39" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21247,11 +21764,11 @@
         <v>2000</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P39" s="5">
         <v>409</v>
@@ -21270,16 +21787,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>1191</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>1192</v>
       </c>
       <c r="D40" s="6">
         <v>139</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="F40" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21308,7 +21825,7 @@
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
       <c r="R40" s="5" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="S40" s="8"/>
       <c r="T40" s="5"/>
@@ -21318,16 +21835,16 @@
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>1195</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>1196</v>
       </c>
       <c r="D41" s="6">
         <v>140</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F41" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21353,10 +21870,10 @@
         <v>2007</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
@@ -21380,16 +21897,16 @@
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>1199</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>1200</v>
       </c>
       <c r="D42" s="6">
         <v>141</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F42" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21415,10 +21932,10 @@
         <v>2003</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
@@ -21444,16 +21961,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>1203</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>1204</v>
       </c>
       <c r="D43" s="6">
         <v>142</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="F43" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21479,11 +21996,11 @@
         <v>1962</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="P43" s="5">
         <v>395</v>
@@ -21502,16 +22019,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>1206</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>1207</v>
       </c>
       <c r="D44" s="6">
         <v>143</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F44" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21552,16 +22069,16 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>1208</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>1209</v>
       </c>
       <c r="D45" s="6">
         <v>144</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F45" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21587,10 +22104,10 @@
         <v>2022</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
@@ -21616,16 +22133,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>1211</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>1212</v>
       </c>
       <c r="D46" s="6">
         <v>145</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F46" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21654,7 +22171,7 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
       <c r="R46" s="5" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
@@ -21666,16 +22183,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>1214</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>1215</v>
       </c>
       <c r="D47" s="6">
         <v>146</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F47" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21718,16 +22235,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>1217</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>1218</v>
       </c>
       <c r="D48" s="6">
         <v>147</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F48" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21756,7 +22273,7 @@
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
       <c r="R48" s="5" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="S48" s="8"/>
       <c r="T48" s="5"/>
@@ -21768,16 +22285,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>1221</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>1222</v>
       </c>
       <c r="D49" s="6">
         <v>148</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F49" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21803,11 +22320,11 @@
         <v>1912</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="P49" s="5">
         <v>390</v>
@@ -21826,16 +22343,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>1225</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>1226</v>
       </c>
       <c r="D50" s="6">
         <v>149</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F50" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21864,7 +22381,7 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
       <c r="R50" s="5" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="S50" s="8"/>
       <c r="T50" s="5"/>
@@ -21876,16 +22393,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>1228</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>1229</v>
       </c>
       <c r="D51" s="6">
         <v>150</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F51" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21905,13 +22422,13 @@
         <v>65000</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="L51" s="5">
         <v>2002</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
@@ -21928,16 +22445,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>1231</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>1232</v>
       </c>
       <c r="D52" s="6">
         <v>151</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F52" s="5" t="str">
         <f t="shared" si="0"/>
@@ -21966,7 +22483,7 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
       <c r="R52" s="5" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="S52" s="8"/>
       <c r="T52" s="5"/>
@@ -21976,16 +22493,16 @@
     <row r="53" spans="1:22" ht="19" x14ac:dyDescent="0.2">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>1235</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>1236</v>
       </c>
       <c r="D53" s="6">
         <v>152</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F53" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22014,7 +22531,7 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
       <c r="R53" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S53" s="8"/>
       <c r="T53" s="5"/>
@@ -22024,16 +22541,16 @@
     <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>1238</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>1239</v>
       </c>
       <c r="D54" s="6">
         <v>153</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F54" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22070,16 +22587,16 @@
     <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>1241</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>1242</v>
       </c>
       <c r="D55" s="6">
         <v>154</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F55" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22105,10 +22622,10 @@
         <v>2022</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
@@ -22134,16 +22651,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>1244</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>1245</v>
       </c>
       <c r="D56" s="6">
         <v>155</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F56" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22169,11 +22686,11 @@
         <v>1996</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N56" s="5"/>
       <c r="O56" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P56" s="5">
         <v>408</v>
@@ -22190,16 +22707,16 @@
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>1246</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>1247</v>
       </c>
       <c r="D57" s="6">
         <v>156</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F57" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22219,16 +22736,16 @@
         <v>66829</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="L57" s="9">
         <v>2002</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N57" s="5" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
@@ -22254,16 +22771,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>1250</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>1251</v>
       </c>
       <c r="D58" s="6">
         <v>157</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F58" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22283,17 +22800,17 @@
         <v>40300</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L58" s="5">
         <v>2020</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N58" s="5"/>
       <c r="O58" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P58" s="5">
         <v>407</v>
@@ -22312,16 +22829,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B59" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>1252</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>1253</v>
       </c>
       <c r="D59" s="6">
         <v>158</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F59" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22350,7 +22867,7 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
       <c r="R59" s="5" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="S59" s="8"/>
       <c r="T59" s="5"/>
@@ -22362,10 +22879,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>1256</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>1257</v>
       </c>
       <c r="D60" s="6">
         <v>159</v>
@@ -22400,7 +22917,7 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
       <c r="R60" s="5" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
@@ -22412,16 +22929,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>1259</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>1260</v>
       </c>
       <c r="D61" s="6">
         <v>160</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F61" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22447,11 +22964,11 @@
         <v>2003</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N61" s="5"/>
       <c r="O61" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P61" s="5">
         <v>404</v>
@@ -22470,16 +22987,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>1262</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>1263</v>
       </c>
       <c r="D62" s="6">
         <v>161</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F62" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22522,16 +23039,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>1265</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>1266</v>
       </c>
       <c r="D63" s="6">
         <v>162</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F63" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22551,7 +23068,7 @@
         <v>71608</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="L63" s="5">
         <v>1973</v>
@@ -22574,16 +23091,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B64" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>1269</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>1270</v>
       </c>
       <c r="D64" s="6">
         <v>163</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F64" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22612,7 +23129,7 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
       <c r="R64" s="5" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
@@ -22624,16 +23141,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>1272</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>1273</v>
       </c>
       <c r="D65" s="6">
         <v>164</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F65" s="5" t="str">
         <f t="shared" si="0"/>
@@ -22674,16 +23191,16 @@
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>1275</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>1276</v>
       </c>
       <c r="D66" s="6">
         <v>165</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F66" s="5" t="str">
         <f t="shared" ref="F66:F129" si="2">LOWER(SUBSTITUTE(_xlfn.TEXTBEFORE(E66,", ")," ","_"))</f>
@@ -22709,10 +23226,10 @@
         <v>2017</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
@@ -22738,16 +23255,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>1279</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>1280</v>
       </c>
       <c r="D67" s="6">
         <v>166</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F67" s="5" t="str">
         <f t="shared" si="2"/>
@@ -22776,7 +23293,7 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
       <c r="R67" s="5" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="S67" s="8"/>
       <c r="T67" s="5"/>
@@ -22788,16 +23305,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>1283</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>1284</v>
       </c>
       <c r="D68" s="6">
         <v>167</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F68" s="5" t="str">
         <f t="shared" si="2"/>
@@ -22826,7 +23343,7 @@
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
       <c r="R68" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S68" s="8"/>
       <c r="T68" s="5"/>
@@ -22838,16 +23355,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>1286</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>1287</v>
       </c>
       <c r="D69" s="6">
         <v>168</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F69" s="5" t="str">
         <f t="shared" si="2"/>
@@ -22873,11 +23390,11 @@
         <v>1973</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N69" s="5"/>
       <c r="O69" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="P69" s="5">
         <v>410</v>
@@ -22896,16 +23413,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>1288</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>1289</v>
       </c>
       <c r="D70" s="6">
         <v>169</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F70" s="5" t="str">
         <f t="shared" si="2"/>
@@ -22934,7 +23451,7 @@
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
       <c r="R70" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
@@ -22946,16 +23463,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>1291</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>1292</v>
       </c>
       <c r="D71" s="6">
         <v>170</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F71" s="5" t="str">
         <f t="shared" si="2"/>
@@ -22984,7 +23501,7 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
       <c r="R71" s="5" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="S71" s="8"/>
       <c r="T71" s="5"/>
@@ -22996,16 +23513,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D72" s="6">
         <v>171</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F72" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23025,7 +23542,7 @@
         <v>81441</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="L72" s="5">
         <v>1957</v>
@@ -23048,16 +23565,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B73" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>1298</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>1299</v>
       </c>
       <c r="D73" s="6">
         <v>172</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F73" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23086,7 +23603,7 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
       <c r="R73" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
@@ -23098,16 +23615,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>1301</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>1302</v>
       </c>
       <c r="D74" s="6">
         <v>173</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F74" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23127,7 +23644,7 @@
         <v>68500</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="L74" s="5">
         <v>2014</v>
@@ -23150,16 +23667,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>1305</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>1306</v>
       </c>
       <c r="D75" s="6">
         <v>174</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F75" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23179,7 +23696,7 @@
         <v>69596</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="L75" s="5">
         <v>2003</v>
@@ -23202,16 +23719,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B76" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>1308</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>1309</v>
       </c>
       <c r="D76" s="6">
         <v>175</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F76" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23240,7 +23757,7 @@
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
       <c r="R76" s="5" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="S76" s="8"/>
       <c r="T76" s="5"/>
@@ -23252,16 +23769,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>1311</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>1312</v>
       </c>
       <c r="D77" s="6">
         <v>176</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F77" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23281,17 +23798,17 @@
         <v>36742</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L77" s="5">
         <v>2012</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N77" s="5"/>
       <c r="O77" s="5" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="P77" s="5">
         <v>407</v>
@@ -23308,16 +23825,16 @@
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A78" s="5"/>
       <c r="B78" s="5" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>1314</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>1315</v>
       </c>
       <c r="D78" s="6">
         <v>177</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F78" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23343,10 +23860,10 @@
         <v>2021</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
@@ -23372,16 +23889,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>1318</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>1319</v>
       </c>
       <c r="D79" s="6">
         <v>178</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F79" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23401,13 +23918,13 @@
         <v>67000</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="L79" s="5">
         <v>2008</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
@@ -23422,16 +23939,16 @@
     <row r="80" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A80" s="5"/>
       <c r="B80" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>1320</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>1321</v>
       </c>
       <c r="D80" s="6">
         <v>179</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="F80" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23451,16 +23968,16 @@
         <v>69000</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L80" s="9">
         <v>2002</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
@@ -23486,16 +24003,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B81" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>1323</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1324</v>
       </c>
       <c r="D81" s="6">
         <v>180</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F81" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23538,16 +24055,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>1326</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>1327</v>
       </c>
       <c r="D82" s="6">
         <v>181</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F82" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23576,7 +24093,7 @@
       <c r="P82" s="11"/>
       <c r="Q82" s="11"/>
       <c r="R82" s="5" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="S82" s="8"/>
       <c r="T82" s="5"/>
@@ -23586,16 +24103,16 @@
     <row r="83" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A83" s="5"/>
       <c r="B83" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>1330</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>1331</v>
       </c>
       <c r="D83" s="6">
         <v>182</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F83" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23615,16 +24132,16 @@
         <v>71000</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L83" s="9">
         <v>2017</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
@@ -23650,16 +24167,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>1334</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>1335</v>
       </c>
       <c r="D84" s="6">
         <v>183</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F84" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23679,7 +24196,7 @@
         <v>82500</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="L84" s="5">
         <v>2010</v>
@@ -23700,10 +24217,10 @@
     <row r="85" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A85" s="5"/>
       <c r="B85" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>1338</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>1339</v>
       </c>
       <c r="D85" s="6">
         <v>184</v>
@@ -23748,16 +24265,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B86" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>1340</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>1341</v>
       </c>
       <c r="D86" s="6">
         <v>185</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F86" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23786,7 +24303,7 @@
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
       <c r="R86" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="S86" s="8"/>
       <c r="T86" s="5"/>
@@ -23796,16 +24313,16 @@
     <row r="87" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A87" s="5"/>
       <c r="B87" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>1343</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>1344</v>
       </c>
       <c r="D87" s="6">
         <v>186</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F87" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23844,23 +24361,23 @@
         <v>#VALUE!</v>
       </c>
       <c r="B88" s="5" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>1346</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>1347</v>
       </c>
       <c r="D88" s="6">
         <v>187</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F88" s="5" t="str">
         <f t="shared" si="2"/>
         <v>washington</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>1004</v>
@@ -23878,11 +24395,11 @@
         <v>2008</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N88" s="5"/>
       <c r="O88" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P88" s="5">
         <v>402</v>
@@ -23901,16 +24418,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>1348</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1349</v>
       </c>
       <c r="D89" s="6">
         <v>188</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F89" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23939,7 +24456,7 @@
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
       <c r="R89" s="5" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
@@ -23951,16 +24468,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B90" s="5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>1350</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>1351</v>
       </c>
       <c r="D90" s="6">
         <v>189</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F90" s="5" t="str">
         <f t="shared" si="2"/>
@@ -23980,7 +24497,7 @@
         <v>69143</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="L90" s="5">
         <v>1999</v>
@@ -24003,16 +24520,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>1353</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>1354</v>
       </c>
       <c r="D91" s="6">
         <v>190</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="F91" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24055,16 +24572,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B92" s="5" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>1356</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>1357</v>
       </c>
       <c r="D92" s="6">
         <v>191</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F92" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24084,13 +24601,13 @@
         <v>72220</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="L92" s="5">
         <v>2002</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
@@ -24107,16 +24624,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>1358</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>1359</v>
       </c>
       <c r="D93" s="6">
         <v>192</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F93" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24142,11 +24659,11 @@
         <v>2000</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N93" s="5"/>
       <c r="O93" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P93" s="5">
         <v>391</v>
@@ -24165,16 +24682,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>1360</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>1361</v>
       </c>
       <c r="D94" s="6">
         <v>193</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F94" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24200,11 +24717,11 @@
         <v>1992</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N94" s="5"/>
       <c r="O94" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P94" s="5">
         <v>410</v>
@@ -24223,16 +24740,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>1362</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>1363</v>
       </c>
       <c r="D95" s="6">
         <v>194</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="F95" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24261,7 +24778,7 @@
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
       <c r="R95" s="5" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="S95" s="8"/>
       <c r="T95" s="5"/>
@@ -24273,16 +24790,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>1366</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>1367</v>
       </c>
       <c r="D96" s="6">
         <v>195</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F96" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24302,7 +24819,7 @@
         <v>65515</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="L96" s="5">
         <v>2000</v>
@@ -24323,16 +24840,16 @@
     <row r="97" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A97" s="5"/>
       <c r="B97" s="5" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>1369</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>1370</v>
       </c>
       <c r="D97" s="6">
         <v>196</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F97" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24352,16 +24869,16 @@
         <v>18000</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="L97" s="9">
         <v>2015</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
@@ -24387,16 +24904,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>1374</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>1375</v>
       </c>
       <c r="D98" s="6">
         <v>197</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="F98" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24422,11 +24939,11 @@
         <v>2004</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N98" s="5"/>
       <c r="O98" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P98" s="5">
         <v>396</v>
@@ -24445,16 +24962,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B99" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>1377</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>1378</v>
       </c>
       <c r="D99" s="6">
         <v>198</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F99" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24483,7 +25000,7 @@
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
       <c r="R99" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="S99" s="8"/>
       <c r="T99" s="5"/>
@@ -24495,10 +25012,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="B100" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>1380</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>1381</v>
       </c>
       <c r="D100" s="6">
         <v>199</v>
@@ -24530,11 +25047,11 @@
         <v>2001</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N100" s="5"/>
       <c r="O100" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P100" s="5">
         <v>399</v>
@@ -24553,10 +25070,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="B101" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>1382</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>1383</v>
       </c>
       <c r="D101" s="6">
         <v>200</v>
@@ -24591,7 +25108,7 @@
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
       <c r="R101" s="5" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
@@ -24603,16 +25120,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B102" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>1384</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>1385</v>
       </c>
       <c r="D102" s="6">
         <v>201</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F102" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24638,11 +25155,11 @@
         <v>1994</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N102" s="5"/>
       <c r="O102" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P102" s="5">
         <v>410</v>
@@ -24659,16 +25176,16 @@
     <row r="103" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A103" s="5"/>
       <c r="B103" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>1386</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>1387</v>
       </c>
       <c r="D103" s="6">
         <v>202</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F103" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24688,16 +25205,16 @@
         <v>25218</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="L103" s="9">
         <v>1926</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
@@ -24723,16 +25240,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B104" s="5" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>1389</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>1390</v>
       </c>
       <c r="D104" s="6">
         <v>203</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F104" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24761,7 +25278,7 @@
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
       <c r="R104" s="5" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
@@ -24771,16 +25288,16 @@
     <row r="105" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A105" s="5"/>
       <c r="B105" s="5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>1393</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>1394</v>
       </c>
       <c r="D105" s="6">
         <v>204</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F105" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24806,10 +25323,10 @@
         <v>2021</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
@@ -24835,16 +25352,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B106" s="5" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>1397</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>1398</v>
       </c>
       <c r="D106" s="6">
         <v>205</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F106" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24870,11 +25387,11 @@
         <v>1991</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N106" s="5"/>
       <c r="O106" s="5" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="P106" s="5">
         <v>400</v>
@@ -24893,16 +25410,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>1401</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>1402</v>
       </c>
       <c r="D107" s="6">
         <v>206</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F107" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24945,16 +25462,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B108" s="5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>1403</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>1404</v>
       </c>
       <c r="D108" s="6">
         <v>207</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F108" s="5" t="str">
         <f t="shared" si="2"/>
@@ -24983,7 +25500,7 @@
       <c r="P108" s="5"/>
       <c r="Q108" s="5"/>
       <c r="R108" s="5" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="S108" s="8"/>
       <c r="T108" s="5"/>
@@ -24995,16 +25512,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>1405</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>1406</v>
       </c>
       <c r="D109" s="6">
         <v>208</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F109" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25033,7 +25550,7 @@
       <c r="P109" s="5"/>
       <c r="Q109" s="5"/>
       <c r="R109" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
@@ -25045,16 +25562,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>1407</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>1408</v>
       </c>
       <c r="D110" s="6">
         <v>209</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F110" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25074,17 +25591,17 @@
         <v>39150</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L110" s="5">
         <v>1989</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N110" s="5"/>
       <c r="O110" s="5" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="P110" s="5">
         <v>400</v>
@@ -25103,16 +25620,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B111" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>1409</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>1410</v>
       </c>
       <c r="D111" s="6">
         <v>210</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F111" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25141,7 +25658,7 @@
       <c r="P111" s="5"/>
       <c r="Q111" s="5"/>
       <c r="R111" s="5" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
@@ -25153,16 +25670,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>1412</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>1413</v>
       </c>
       <c r="D112" s="6">
         <v>211</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F112" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25191,7 +25708,7 @@
       <c r="P112" s="5"/>
       <c r="Q112" s="5"/>
       <c r="R112" s="5" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
@@ -25201,16 +25718,16 @@
     <row r="113" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A113" s="5"/>
       <c r="B113" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>1414</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>1415</v>
       </c>
       <c r="D113" s="6">
         <v>212</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F113" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25236,10 +25753,10 @@
         <v>2008</v>
       </c>
       <c r="M113" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N113" s="5" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
@@ -25265,16 +25782,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B114" s="5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C114" s="5" t="s">
         <v>1417</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>1418</v>
       </c>
       <c r="D114" s="6">
         <v>213</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F114" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25303,7 +25820,7 @@
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
       <c r="R114" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="S114" s="8"/>
       <c r="T114" s="5"/>
@@ -25315,16 +25832,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B115" s="5" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>1419</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>1420</v>
       </c>
       <c r="D115" s="6">
         <v>214</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F115" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25353,7 +25870,7 @@
       <c r="P115" s="5"/>
       <c r="Q115" s="5"/>
       <c r="R115" s="5" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
@@ -25363,16 +25880,16 @@
     <row r="116" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A116" s="5"/>
       <c r="B116" s="5" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>1423</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>1424</v>
       </c>
       <c r="D116" s="6">
         <v>215</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F116" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25398,10 +25915,10 @@
         <v>2012</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N116" s="5" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
@@ -25427,16 +25944,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B117" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>1426</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>1427</v>
       </c>
       <c r="D117" s="6">
         <v>216</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F117" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25465,7 +25982,7 @@
       <c r="P117" s="5"/>
       <c r="Q117" s="5"/>
       <c r="R117" s="5" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="S117" s="8"/>
       <c r="T117" s="5"/>
@@ -25475,16 +25992,16 @@
     <row r="118" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A118" s="5"/>
       <c r="B118" s="5" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>1428</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>1429</v>
       </c>
       <c r="D118" s="6">
         <v>217</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="F118" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25510,10 +26027,10 @@
         <v>2022</v>
       </c>
       <c r="M118" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N118" s="5" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
@@ -25539,16 +26056,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>1431</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>1432</v>
       </c>
       <c r="D119" s="6">
         <v>218</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F119" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25568,7 +26085,7 @@
         <v>70240</v>
       </c>
       <c r="K119" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="L119" s="5">
         <v>2020</v>
@@ -25589,16 +26106,16 @@
     <row r="120" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A120" s="5"/>
       <c r="B120" s="5" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>1433</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>1434</v>
       </c>
       <c r="D120" s="6">
         <v>219</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F120" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25624,10 +26141,10 @@
         <v>1924</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N120" s="5" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
@@ -25653,16 +26170,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>1436</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>1437</v>
       </c>
       <c r="D121" s="6">
         <v>220</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F121" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25691,7 +26208,7 @@
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
       <c r="R121" s="5" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="S121" s="8"/>
       <c r="T121" s="5"/>
@@ -25701,16 +26218,16 @@
     <row r="122" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
       <c r="B122" s="5" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C122" s="5" t="s">
         <v>1439</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>1440</v>
       </c>
       <c r="D122" s="6">
         <v>221</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F122" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25736,10 +26253,10 @@
         <v>2010</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N122" s="5" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
@@ -25765,16 +26282,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B123" s="5" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>1443</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>1444</v>
       </c>
       <c r="D123" s="6">
         <v>222</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F123" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25803,7 +26320,7 @@
       <c r="P123" s="5"/>
       <c r="Q123" s="5"/>
       <c r="R123" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="S123" s="8"/>
       <c r="T123" s="5"/>
@@ -25815,16 +26332,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B124" s="5" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C124" s="5" t="s">
         <v>1445</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>1446</v>
       </c>
       <c r="D124" s="6">
         <v>223</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F124" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25850,7 +26367,7 @@
         <v>2006</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
@@ -25865,16 +26382,16 @@
     <row r="125" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A125" s="5"/>
       <c r="B125" s="5" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>1448</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>1449</v>
       </c>
       <c r="D125" s="6">
         <v>224</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F125" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25900,10 +26417,10 @@
         <v>2010</v>
       </c>
       <c r="M125" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N125" s="5" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
@@ -25929,16 +26446,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C126" s="5" t="s">
         <v>1452</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>1453</v>
       </c>
       <c r="D126" s="6">
         <v>225</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F126" s="5" t="str">
         <f t="shared" si="2"/>
@@ -25964,11 +26481,11 @@
         <v>2000</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N126" s="5"/>
       <c r="O126" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P126" s="5">
         <v>403</v>
@@ -25987,10 +26504,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="B127" s="5" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>1455</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>1456</v>
       </c>
       <c r="D127" s="6">
         <v>226</v>
@@ -26025,7 +26542,7 @@
       <c r="P127" s="5"/>
       <c r="Q127" s="5"/>
       <c r="R127" s="5" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="S127" s="5"/>
       <c r="T127" s="5"/>
@@ -26037,16 +26554,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B128" s="5" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>1457</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>1458</v>
       </c>
       <c r="D128" s="6">
         <v>227</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="F128" s="5" t="str">
         <f t="shared" si="2"/>
@@ -26072,11 +26589,11 @@
         <v>1999</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N128" s="5"/>
       <c r="O128" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P128" s="5">
         <v>401</v>
@@ -26095,16 +26612,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B129" s="5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>1459</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>1460</v>
       </c>
       <c r="D129" s="6">
         <v>228</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F129" s="5" t="str">
         <f t="shared" si="2"/>
@@ -26133,7 +26650,7 @@
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
       <c r="R129" s="5" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="S129" s="8"/>
       <c r="T129" s="5"/>
@@ -26145,16 +26662,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>1463</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>1464</v>
       </c>
       <c r="D130" s="6">
         <v>229</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F130" s="5" t="str">
         <f t="shared" ref="F130:F142" si="4">LOWER(SUBSTITUTE(_xlfn.TEXTBEFORE(E130,", ")," ","_"))</f>
@@ -26180,11 +26697,11 @@
         <v>2010</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N130" s="5"/>
       <c r="O130" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P130" s="5">
         <v>404</v>
@@ -26203,16 +26720,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B131" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>1465</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>1466</v>
       </c>
       <c r="D131" s="6">
         <v>230</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F131" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26241,7 +26758,7 @@
       <c r="P131" s="5"/>
       <c r="Q131" s="5"/>
       <c r="R131" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="S131" s="8"/>
       <c r="T131" s="5"/>
@@ -26253,16 +26770,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B132" s="5" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>1467</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>1468</v>
       </c>
       <c r="D132" s="6">
         <v>231</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F132" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26291,7 +26808,7 @@
       <c r="P132" s="5"/>
       <c r="Q132" s="5"/>
       <c r="R132" s="5" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="S132" s="8"/>
       <c r="T132" s="5"/>
@@ -26301,16 +26818,16 @@
     <row r="133" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
       <c r="B133" s="5" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>1470</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>1471</v>
       </c>
       <c r="D133" s="6">
         <v>232</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F133" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26336,10 +26853,10 @@
         <v>2005</v>
       </c>
       <c r="M133" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N133" s="5" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
@@ -26363,16 +26880,16 @@
     <row r="134" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
       <c r="B134" s="5" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>1474</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>1475</v>
       </c>
       <c r="D134" s="6">
         <v>233</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F134" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26392,16 +26909,16 @@
         <v>26000</v>
       </c>
       <c r="K134" s="5" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L134" s="9">
         <v>2021</v>
       </c>
       <c r="M134" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N134" s="5" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
@@ -26427,16 +26944,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B135" s="5" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>1477</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>1478</v>
       </c>
       <c r="D135" s="6">
         <v>234</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F135" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26462,11 +26979,11 @@
         <v>2017</v>
       </c>
       <c r="M135" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N135" s="5"/>
       <c r="O135" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P135" s="5">
         <v>400</v>
@@ -26485,16 +27002,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B136" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>1480</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>1481</v>
       </c>
       <c r="D136" s="6">
         <v>235</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F136" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26514,7 +27031,7 @@
         <v>66655</v>
       </c>
       <c r="K136" s="5" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="L136" s="5">
         <v>2016</v>
@@ -26537,16 +27054,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B137" s="5" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>1483</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>1484</v>
       </c>
       <c r="D137" s="6">
         <v>236</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="F137" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26575,7 +27092,7 @@
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
       <c r="R137" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="S137" s="5"/>
       <c r="T137" s="5"/>
@@ -26587,16 +27104,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B138" s="5" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>1486</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>1487</v>
       </c>
       <c r="D138" s="6">
         <v>237</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F138" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26625,7 +27142,7 @@
       <c r="P138" s="5"/>
       <c r="Q138" s="5"/>
       <c r="R138" s="5" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="S138" s="8"/>
       <c r="T138" s="5"/>
@@ -26635,16 +27152,16 @@
     <row r="139" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A139" s="5"/>
       <c r="B139" s="5" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>1488</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>1489</v>
       </c>
       <c r="D139" s="6">
         <v>238</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F139" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26683,16 +27200,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B140" s="5" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>1490</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>1491</v>
       </c>
       <c r="D140" s="6">
         <v>239</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F140" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26718,11 +27235,11 @@
         <v>1914</v>
       </c>
       <c r="M140" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N140" s="5"/>
       <c r="O140" s="5" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="P140" s="5">
         <v>400</v>
@@ -26741,16 +27258,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B141" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C141" s="5" t="s">
         <v>1492</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>1493</v>
       </c>
       <c r="D141" s="6">
         <v>240</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F141" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26779,7 +27296,7 @@
       <c r="P141" s="5"/>
       <c r="Q141" s="5"/>
       <c r="R141" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="S141" s="8"/>
       <c r="T141" s="5"/>
@@ -26791,16 +27308,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="B142" s="5" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>1494</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>1495</v>
       </c>
       <c r="D142" s="6">
         <v>241</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="F142" s="5" t="str">
         <f t="shared" si="4"/>
@@ -26826,13 +27343,13 @@
         <v>2009</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="N142" s="5" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="O142" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P142" s="5">
         <v>408</v>
@@ -26858,22 +27375,22 @@
     </row>
     <row r="143" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="B143" s="13" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C143" t="s">
         <v>1550</v>
-      </c>
-      <c r="C143" t="s">
-        <v>1551</v>
       </c>
       <c r="D143">
         <v>242</v>
       </c>
       <c r="E143" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="F143" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G143" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H143" t="s">
         <v>975</v>
@@ -26890,22 +27407,26 @@
     </row>
     <row r="144" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="13" t="s">
-        <v>1552</v>
+        <v>1551</v>
+      </c>
+      <c r="C144" t="str">
+        <f>SUBSTITUTE(LOWER(B144)," ","_")</f>
+        <v>arun_jaitley_cricket_stadium</v>
       </c>
       <c r="D144">
         <v>243</v>
       </c>
       <c r="E144" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="F144" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="G144" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H144" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="I144" t="s">
         <v>976</v>
@@ -26917,24 +27438,28 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="145" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B145" s="13" t="s">
-        <v>1553</v>
+        <v>1552</v>
+      </c>
+      <c r="C145" t="str">
+        <f t="shared" ref="C145:C158" si="6">SUBSTITUTE(LOWER(B145)," ","_")</f>
+        <v>narendra_modi_stadium</v>
       </c>
       <c r="D145">
         <v>244</v>
       </c>
       <c r="E145" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="F145" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G145" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H145" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="I145" t="s">
         <v>976</v>
@@ -26946,24 +27471,28 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
-        <v>1554</v>
+        <v>1553</v>
+      </c>
+      <c r="C146" t="str">
+        <f t="shared" si="6"/>
+        <v>eden_gardens</v>
       </c>
       <c r="D146">
         <v>245</v>
       </c>
       <c r="E146" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="F146" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="G146" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H146" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="I146" t="s">
         <v>976</v>
@@ -26975,24 +27504,28 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="147" spans="2:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B147" s="13" t="s">
-        <v>1555</v>
+        <v>1554</v>
+      </c>
+      <c r="C147" t="str">
+        <f t="shared" si="6"/>
+        <v>ekana_cricket_stadium</v>
       </c>
       <c r="D147">
         <v>246</v>
       </c>
       <c r="E147" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="F147" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="G147" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H147" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="I147" t="s">
         <v>976</v>
@@ -27004,24 +27537,28 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="148" spans="2:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B148" s="13" t="s">
-        <v>1556</v>
+        <v>1555</v>
+      </c>
+      <c r="C148" t="str">
+        <f t="shared" si="6"/>
+        <v>wankhede_stadium</v>
       </c>
       <c r="D148">
         <v>247</v>
       </c>
       <c r="E148" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="F148" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H148" t="s">
         <v>1502</v>
-      </c>
-      <c r="G148" t="s">
-        <v>1539</v>
-      </c>
-      <c r="H148" t="s">
-        <v>1503</v>
       </c>
       <c r="I148" t="s">
         <v>976</v>
@@ -27033,24 +27570,28 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="149" spans="2:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:13" ht="34" x14ac:dyDescent="0.2">
       <c r="B149" s="13" t="s">
-        <v>1557</v>
+        <v>1556</v>
+      </c>
+      <c r="C149" t="str">
+        <f t="shared" si="6"/>
+        <v>maharaja_yadavindra_singh_international_cricket_stadium</v>
       </c>
       <c r="D149">
         <v>248</v>
       </c>
       <c r="E149" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="F149" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H149" t="s">
         <v>1528</v>
-      </c>
-      <c r="G149" t="s">
-        <v>1521</v>
-      </c>
-      <c r="H149" t="s">
-        <v>1529</v>
       </c>
       <c r="I149" t="s">
         <v>976</v>
@@ -27062,24 +27603,28 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="150" spans="2:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B150" s="13" t="s">
-        <v>1558</v>
+        <v>1557</v>
+      </c>
+      <c r="C150" t="str">
+        <f t="shared" si="6"/>
+        <v>sawai_mansingh_stadium</v>
       </c>
       <c r="D150">
         <v>249</v>
       </c>
       <c r="E150" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="F150" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H150" t="s">
         <v>1530</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1522</v>
-      </c>
-      <c r="H150" t="s">
-        <v>1531</v>
       </c>
       <c r="I150" t="s">
         <v>976</v>
@@ -27091,24 +27636,28 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="151" spans="2:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B151" s="13" t="s">
-        <v>1559</v>
+        <v>1558</v>
+      </c>
+      <c r="C151" t="str">
+        <f t="shared" si="6"/>
+        <v>m._chinnaswamy_stadium</v>
       </c>
       <c r="D151">
         <v>250</v>
       </c>
       <c r="E151" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F151" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="G151" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H151" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="I151" t="s">
         <v>976</v>
@@ -27120,24 +27669,28 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="152" spans="2:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:13" ht="34" x14ac:dyDescent="0.2">
       <c r="B152" s="13" t="s">
-        <v>1560</v>
+        <v>1559</v>
+      </c>
+      <c r="C152" t="str">
+        <f t="shared" si="6"/>
+        <v>rajiv_gandhi_international_cricket_("uppal")_stadium</v>
       </c>
       <c r="D152">
         <v>251</v>
       </c>
       <c r="E152" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="F152" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G152" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H152" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="I152" t="s">
         <v>976</v>
@@ -27147,6 +27700,141 @@
       </c>
       <c r="L152">
         <v>2003</v>
+      </c>
+    </row>
+    <row r="153" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B153" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C153" t="str">
+        <f t="shared" si="6"/>
+        <v>oakland_coliseum</v>
+      </c>
+      <c r="D153">
+        <v>252</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H153" t="s">
+        <v>988</v>
+      </c>
+      <c r="I153" t="s">
+        <v>378</v>
+      </c>
+      <c r="J153" s="14">
+        <v>12000</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L153">
+        <v>1966</v>
+      </c>
+      <c r="M153" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="154" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B154" s="13" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C154" t="str">
+        <f t="shared" si="6"/>
+        <v>grand_prairie_stadium</v>
+      </c>
+      <c r="D154">
+        <v>253</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1579</v>
+      </c>
+      <c r="H154" t="s">
+        <v>977</v>
+      </c>
+      <c r="I154" t="s">
+        <v>378</v>
+      </c>
+      <c r="J154" s="14">
+        <v>7200</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L154">
+        <v>2008</v>
+      </c>
+      <c r="M154" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="155" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B155" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C155" t="str">
+        <f t="shared" si="6"/>
+        <v>knight_riders_cricket_field_at_fairplex</v>
+      </c>
+      <c r="D155">
+        <v>254</v>
+      </c>
+      <c r="E155" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H155" t="s">
+        <v>988</v>
+      </c>
+      <c r="I155" t="s">
+        <v>378</v>
+      </c>
+      <c r="J155" s="14">
+        <v>5000</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L155">
+        <v>2026</v>
+      </c>
+      <c r="M155" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="156" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C156" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C157" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C158" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
     </row>
   </sheetData>
